--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win\Documents\Django_JUNEJULY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\newdata\gitrepo\itp\ITPM-Django-JUNE-JULY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B45D3CAD-CF12-451B-B0BC-94FD0DD1FFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{87CBDD44-6124-4F07-BD9F-5942814D11CF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="168">
   <si>
     <t>Sr. No</t>
   </si>
@@ -544,7 +543,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1069,16 +1068,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDE5004-8844-4AB5-BEF2-561DDA8CC074}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="38.21875" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="38.1796875" customWidth="1"/>
+    <col min="5" max="5" width="33.36328125" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1115,7 +1114,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1131,11 +1130,8 @@
       <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1151,11 +1147,8 @@
       <c r="E4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:7" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1171,11 +1164,8 @@
       <c r="E5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1191,11 +1181,8 @@
       <c r="E6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1218,7 +1205,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1235,10 +1222,10 @@
         <v>7</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1255,10 +1242,10 @@
         <v>7</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1278,7 +1265,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1294,11 +1281,8 @@
       <c r="E11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1314,11 +1298,8 @@
       <c r="E12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1334,11 +1315,8 @@
       <c r="E13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1354,8 +1332,11 @@
       <c r="E14" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1371,11 +1352,8 @@
       <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1395,7 +1373,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1415,7 +1393,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1431,11 +1409,8 @@
       <c r="E18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1451,11 +1426,8 @@
       <c r="E19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1471,11 +1443,8 @@
       <c r="E20" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1495,7 +1464,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1511,14 +1480,11 @@
       <c r="E22" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="I22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1534,11 +1500,8 @@
       <c r="E23" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1558,7 +1521,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="77.400000000000006" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1578,7 +1541,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1594,11 +1557,8 @@
       <c r="E26" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1614,11 +1574,8 @@
       <c r="E27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1638,7 +1595,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1654,11 +1611,8 @@
       <c r="E29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1678,7 +1632,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1695,13 +1649,13 @@
         <v>7</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1717,11 +1671,8 @@
       <c r="E32" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1737,11 +1688,8 @@
       <c r="E33" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="39.6" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:6" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1757,11 +1705,8 @@
       <c r="E34" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1781,7 +1726,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1797,11 +1742,8 @@
       <c r="E36" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1818,10 +1760,10 @@
         <v>7</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1838,10 +1780,10 @@
         <v>7</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1858,10 +1800,10 @@
         <v>7</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1877,11 +1819,8 @@
       <c r="E40" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1898,10 +1837,10 @@
         <v>7</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1917,11 +1856,8 @@
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1941,7 +1877,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1958,10 +1894,10 @@
         <v>7</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="39.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1977,11 +1913,8 @@
       <c r="E45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1997,11 +1930,8 @@
       <c r="E46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2017,11 +1947,8 @@
       <c r="E47" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F47" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2037,11 +1964,8 @@
       <c r="E48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2061,7 +1985,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="39.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2081,7 +2005,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2097,11 +2021,8 @@
       <c r="E51" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2121,7 +2042,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2141,7 +2062,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2158,10 +2079,10 @@
         <v>106</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2177,11 +2098,8 @@
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2198,10 +2116,10 @@
         <v>106</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2218,13 +2136,13 @@
         <v>106</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G57" s="15" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2244,7 +2162,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2264,7 +2182,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2281,10 +2199,10 @@
         <v>7</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2301,10 +2219,10 @@
         <v>7</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2321,10 +2239,10 @@
         <v>7</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2340,11 +2258,8 @@
       <c r="E63" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F63" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2361,10 +2276,10 @@
         <v>106</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2384,7 +2299,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2401,10 +2316,10 @@
         <v>106</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2420,11 +2335,8 @@
       <c r="E67" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F67" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2440,11 +2352,8 @@
       <c r="E68" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2464,7 +2373,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2484,7 +2393,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2504,7 +2413,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2524,7 +2433,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2544,7 +2453,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2564,7 +2473,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2584,7 +2493,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="52.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2602,7 +2511,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="64.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <v>76</v>
       </c>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="168">
   <si>
     <t>Sr. No</t>
   </si>
@@ -525,9 +525,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
     <t>p</t>
   </si>
   <si>
@@ -538,6 +535,9 @@
   </si>
   <si>
     <t>Offline(java)</t>
+  </si>
+  <si>
+    <t>Tanvi</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -703,11 +703,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -749,12 +825,31 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,15 +1164,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" customWidth="1"/>
     <col min="6" max="6" width="12.54296875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1093,8 +1189,18 @@
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F1" s="25">
+        <v>46037</v>
+      </c>
+      <c r="G1" s="25">
+        <v>46038</v>
+      </c>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1113,8 +1219,17 @@
       <c r="F2" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G2" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1130,8 +1245,12 @@
       <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1147,8 +1266,12 @@
       <c r="E4" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="5" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1164,8 +1287,12 @@
       <c r="E5" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1181,8 +1308,12 @@
       <c r="E6" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1201,11 +1332,17 @@
       <c r="F7" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G7" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1224,8 +1361,12 @@
       <c r="F8" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="9" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1244,8 +1385,17 @@
       <c r="F9" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G9" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+    </row>
+    <row r="10" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1264,8 +1414,17 @@
       <c r="F10" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="28" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G10" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:11" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1281,8 +1440,12 @@
       <c r="E11" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1298,8 +1461,12 @@
       <c r="E12" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1315,8 +1482,17 @@
       <c r="E13" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G13" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1335,8 +1511,17 @@
       <c r="F14" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G14" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1352,8 +1537,12 @@
       <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1372,8 +1561,17 @@
       <c r="F16" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G16" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1392,8 +1590,17 @@
       <c r="F17" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G17" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1409,8 +1616,14 @@
       <c r="E18" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H18" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1426,8 +1639,12 @@
       <c r="E19" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1443,8 +1660,12 @@
       <c r="E20" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1463,8 +1684,17 @@
       <c r="F21" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G21" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1480,11 +1710,14 @@
       <c r="E22" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I22">
+      <c r="H22" s="14"/>
+      <c r="I22" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1500,8 +1733,14 @@
       <c r="E23" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H23" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1520,8 +1759,17 @@
       <c r="F24" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G24" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+    </row>
+    <row r="25" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1540,8 +1788,17 @@
       <c r="F25" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G25" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1557,8 +1814,12 @@
       <c r="E26" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1574,8 +1835,17 @@
       <c r="E27" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G27" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1594,8 +1864,15 @@
       <c r="F28" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G28" s="24"/>
+      <c r="H28" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1611,8 +1888,12 @@
       <c r="E29" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1631,8 +1912,17 @@
       <c r="F30" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G30" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+    </row>
+    <row r="31" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1651,11 +1941,17 @@
       <c r="F31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G31" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+    </row>
+    <row r="32" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1671,8 +1967,12 @@
       <c r="E32" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+    </row>
+    <row r="33" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1688,8 +1988,12 @@
       <c r="E33" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1705,8 +2009,17 @@
       <c r="E34" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G34" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1725,8 +2038,17 @@
       <c r="F35" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G35" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+    </row>
+    <row r="36" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1742,8 +2064,12 @@
       <c r="E36" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1762,8 +2088,17 @@
       <c r="F37" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G37" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+    </row>
+    <row r="38" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1782,8 +2117,17 @@
       <c r="F38" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G38" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+    </row>
+    <row r="39" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1802,8 +2146,17 @@
       <c r="F39" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G39" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+    </row>
+    <row r="40" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1819,8 +2172,15 @@
       <c r="E40" s="11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G40" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+    </row>
+    <row r="41" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1839,8 +2199,12 @@
       <c r="F41" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+    </row>
+    <row r="42" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1856,8 +2220,17 @@
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G42" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1876,8 +2249,17 @@
       <c r="F43" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G43" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1896,8 +2278,17 @@
       <c r="F44" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G44" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="45" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1913,8 +2304,15 @@
       <c r="E45" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G45" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+    </row>
+    <row r="46" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1930,13 +2328,19 @@
       <c r="E46" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H46" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+    </row>
+    <row r="47" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C47" s="3">
         <v>8624085161</v>
@@ -1945,10 +2349,22 @@
         <v>98</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+        <v>164</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -1964,8 +2380,12 @@
       <c r="E48" s="12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="49" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -1984,8 +2404,12 @@
       <c r="F49" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+    </row>
+    <row r="50" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -1999,13 +2423,17 @@
         <v>105</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+    </row>
+    <row r="51" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2021,8 +2449,18 @@
       <c r="E51" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F51" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+    </row>
+    <row r="52" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2041,8 +2479,12 @@
       <c r="F52" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+    </row>
+    <row r="53" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2061,8 +2503,12 @@
       <c r="F53" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+    </row>
+    <row r="54" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2078,11 +2524,14 @@
       <c r="E54" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F54" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H54" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+    </row>
+    <row r="55" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2098,8 +2547,14 @@
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H55" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+    </row>
+    <row r="56" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2115,11 +2570,12 @@
       <c r="E56" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F56" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+    </row>
+    <row r="57" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2138,11 +2594,15 @@
       <c r="F57" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G57" s="15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G57" s="23"/>
+      <c r="H57" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+    </row>
+    <row r="58" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2161,8 +2621,14 @@
       <c r="F58" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H58" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+    </row>
+    <row r="59" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2181,8 +2647,12 @@
       <c r="F59" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+    </row>
+    <row r="60" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2201,8 +2671,14 @@
       <c r="F60" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H60" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+    </row>
+    <row r="61" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2218,11 +2694,12 @@
       <c r="E61" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F61" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+    </row>
+    <row r="62" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2241,8 +2718,17 @@
       <c r="F62" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G62" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+    </row>
+    <row r="63" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2258,8 +2744,14 @@
       <c r="E63" s="13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H63" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+    </row>
+    <row r="64" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -2276,10 +2768,17 @@
         <v>106</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+        <v>163</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+    </row>
+    <row r="65" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2298,8 +2797,12 @@
       <c r="F65" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+    </row>
+    <row r="66" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2315,11 +2818,12 @@
       <c r="E66" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F66" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
+    </row>
+    <row r="67" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2335,8 +2839,18 @@
       <c r="E67" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F67" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
+    </row>
+    <row r="68" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2352,8 +2866,12 @@
       <c r="E68" s="10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+    </row>
+    <row r="69" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2372,8 +2890,17 @@
       <c r="F69" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G69" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+    </row>
+    <row r="70" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2392,8 +2919,17 @@
       <c r="F70" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G70" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+    </row>
+    <row r="71" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2412,8 +2948,17 @@
       <c r="F71" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G71" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+    </row>
+    <row r="72" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2432,8 +2977,15 @@
       <c r="F72" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G72" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+    </row>
+    <row r="73" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2452,8 +3004,17 @@
       <c r="F73" s="14" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G73" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+    </row>
+    <row r="74" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2467,13 +3028,19 @@
         <v>154</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F74" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H74" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+    </row>
+    <row r="75" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2492,8 +3059,12 @@
       <c r="F75" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+    </row>
+    <row r="76" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2510,26 +3081,56 @@
       <c r="F76" s="14" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="2">
+      <c r="G76" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
+    </row>
+    <row r="77" spans="1:12" ht="68" x14ac:dyDescent="0.35">
+      <c r="A77" s="15">
         <v>76</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="17">
         <v>8237450604</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F77" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F77" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+    </row>
+    <row r="78" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="14">
+        <v>77</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="L78" s="22"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F79" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="166">
   <si>
     <t>Sr. No</t>
   </si>
@@ -520,12 +520,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>p</t>
   </si>
   <si>
     <t>online</t>
@@ -1190,11 +1184,9 @@
         <v>4</v>
       </c>
       <c r="F1" s="25">
-        <v>46037</v>
-      </c>
-      <c r="G1" s="25">
-        <v>46038</v>
-      </c>
+        <v>46042</v>
+      </c>
+      <c r="G1" s="25"/>
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
@@ -1219,12 +1211,8 @@
       <c r="F2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="14"/>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
@@ -1329,15 +1317,8 @@
       <c r="E7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G7" s="23"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
@@ -1357,9 +1338,6 @@
       </c>
       <c r="E8" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>161</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
@@ -1382,15 +1360,7 @@
       <c r="E9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
@@ -1414,12 +1384,8 @@
       <c r="F10" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
@@ -1482,12 +1448,11 @@
       <c r="E13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F13" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="14"/>
@@ -1508,15 +1473,8 @@
       <c r="E14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G14" s="23"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
@@ -1558,15 +1516,8 @@
       <c r="E16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G16" s="23"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
@@ -1587,15 +1538,8 @@
       <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="14"/>
@@ -1616,9 +1560,7 @@
       <c r="E18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
@@ -1684,12 +1626,8 @@
       <c r="F21" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G21" s="24"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
@@ -1733,9 +1671,7 @@
       <c r="E23" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H23" s="14"/>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
       <c r="K23" s="14"/>
@@ -1759,12 +1695,8 @@
       <c r="F24" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G24" s="24"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
@@ -1788,12 +1720,8 @@
       <c r="F25" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G25" s="24"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
@@ -1835,12 +1763,11 @@
       <c r="E27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F27" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="24"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="K27" s="14"/>
@@ -1865,9 +1792,7 @@
         <v>161</v>
       </c>
       <c r="G28" s="24"/>
-      <c r="H28" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="K28" s="14"/>
@@ -1887,6 +1812,9 @@
       </c>
       <c r="E29" s="11" t="s">
         <v>7</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
@@ -1912,12 +1840,8 @@
       <c r="F30" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G30" s="24"/>
+      <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
@@ -1941,12 +1865,8 @@
       <c r="F31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G31" s="24"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
       <c r="K31" s="14"/>
@@ -2009,12 +1929,11 @@
       <c r="E34" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F34" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="24"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
       <c r="K34" s="14"/>
@@ -2038,12 +1957,8 @@
       <c r="F35" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G35" s="24"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
       <c r="K35" s="14"/>
@@ -2063,6 +1978,9 @@
       </c>
       <c r="E36" s="11" t="s">
         <v>7</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
@@ -2088,12 +2006,8 @@
       <c r="F37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G37" s="24"/>
+      <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
@@ -2114,15 +2028,8 @@
       <c r="E38" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G38" s="24"/>
+      <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
       <c r="K38" s="14"/>
@@ -2146,12 +2053,8 @@
       <c r="F39" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G39" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G39" s="24"/>
+      <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
       <c r="K39" s="14"/>
@@ -2172,9 +2075,10 @@
       <c r="E40" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="24" t="s">
-        <v>161</v>
-      </c>
+      <c r="F40" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G40" s="24"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
@@ -2196,9 +2100,6 @@
       <c r="E41" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="14" t="s">
-        <v>161</v>
-      </c>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
@@ -2220,12 +2121,8 @@
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G42" s="24"/>
+      <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
       <c r="K42" s="14"/>
@@ -2249,12 +2146,8 @@
       <c r="F43" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G43" s="24"/>
+      <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
       <c r="K43" s="14"/>
@@ -2278,12 +2171,8 @@
       <c r="F44" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G44" s="24"/>
+      <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="K44" s="14"/>
@@ -2304,9 +2193,10 @@
       <c r="E45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="24" t="s">
-        <v>161</v>
-      </c>
+      <c r="F45" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="24"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
@@ -2328,9 +2218,7 @@
       <c r="E46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
       <c r="K46" s="14"/>
@@ -2340,7 +2228,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C47" s="3">
         <v>8624085161</v>
@@ -2349,17 +2237,13 @@
         <v>98</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G47" s="24"/>
+      <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
       <c r="K47" s="14"/>
@@ -2402,7 +2286,7 @@
         <v>103</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
@@ -2423,10 +2307,7 @@
         <v>105</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
@@ -2449,12 +2330,7 @@
       <c r="E51" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>161</v>
-      </c>
+      <c r="G51" s="23"/>
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
@@ -2476,9 +2352,6 @@
       <c r="E52" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F52" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
@@ -2500,9 +2373,6 @@
       <c r="E53" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F53" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14"/>
@@ -2524,9 +2394,7 @@
       <c r="E54" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14"/>
       <c r="K54" s="14"/>
@@ -2547,9 +2415,10 @@
       <c r="E55" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H55" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F55" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="14"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="K55" s="14"/>
@@ -2591,13 +2460,8 @@
       <c r="E57" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F57" s="14" t="s">
-        <v>161</v>
-      </c>
       <c r="G57" s="23"/>
-      <c r="H57" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
       <c r="K57" s="14"/>
@@ -2618,12 +2482,7 @@
       <c r="E58" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F58" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
       <c r="K58" s="14"/>
@@ -2643,9 +2502,6 @@
       </c>
       <c r="E59" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
@@ -2671,9 +2527,7 @@
       <c r="F60" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H60" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
       <c r="K60" s="14"/>
@@ -2715,15 +2569,7 @@
       <c r="E62" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F62" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
       <c r="K62" s="14"/>
@@ -2744,9 +2590,10 @@
       <c r="E63" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H63" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F63" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
       <c r="K63" s="14"/>
@@ -2767,12 +2614,7 @@
       <c r="E64" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F64" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>161</v>
-      </c>
+      <c r="G64" s="23"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
@@ -2794,9 +2636,6 @@
       <c r="E65" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F65" s="14" t="s">
-        <v>162</v>
-      </c>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
@@ -2839,12 +2678,7 @@
       <c r="E67" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F67" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>161</v>
-      </c>
+      <c r="G67" s="23"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
@@ -2890,12 +2724,8 @@
       <c r="F69" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G69" s="23"/>
+      <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
       <c r="K69" s="14"/>
@@ -2919,12 +2749,8 @@
       <c r="F70" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G70" s="23"/>
+      <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
       <c r="K70" s="14"/>
@@ -2948,12 +2774,8 @@
       <c r="F71" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G71" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G71" s="23"/>
+      <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
       <c r="K71" s="14"/>
@@ -2975,11 +2797,9 @@
         <v>106</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>161</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G72" s="23"/>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
@@ -3004,12 +2824,8 @@
       <c r="F73" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G73" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="G73" s="23"/>
+      <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
@@ -3028,14 +2844,9 @@
         <v>154</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F74" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="H74" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="H74" s="14"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
@@ -3055,9 +2866,6 @@
       </c>
       <c r="E75" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
@@ -3079,14 +2887,10 @@
         <v>103</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="14" t="s">
-        <v>161</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G76" s="23"/>
+      <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
@@ -3107,25 +2911,19 @@
       <c r="E77" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F77" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G77" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="F77" s="19"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
       <c r="K77" s="14"/>
     </row>
-    <row r="78" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" s="14" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="14">
         <v>77</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L78" s="22"/>
     </row>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -532,6 +532,9 @@
   </si>
   <si>
     <t>Tanvi</t>
+  </si>
+  <si>
+    <t>Sanket Kunde</t>
   </si>
 </sst>
 </file>
@@ -596,7 +599,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,6 +615,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -840,10 +849,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1158,13 +1173,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" customWidth="1"/>
     <col min="6" max="6" width="12.54296875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
@@ -1183,10 +1198,12 @@
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25">
+      <c r="F1" s="24">
         <v>46042</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="25">
+        <v>46043</v>
+      </c>
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
@@ -1211,7 +1228,9 @@
       <c r="F2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="23"/>
+      <c r="G2" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
@@ -1317,7 +1336,7 @@
       <c r="E7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
@@ -1384,7 +1403,9 @@
       <c r="F10" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
@@ -1451,7 +1472,9 @@
       <c r="F13" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -1473,7 +1496,9 @@
       <c r="E14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="23"/>
+      <c r="G14" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
@@ -1516,7 +1541,7 @@
       <c r="E16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -1538,7 +1563,7 @@
       <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -1626,7 +1651,9 @@
       <c r="F21" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="24"/>
+      <c r="G21" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
@@ -1695,7 +1722,9 @@
       <c r="F24" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="24"/>
+      <c r="G24" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
@@ -1720,7 +1749,9 @@
       <c r="F25" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="24"/>
+      <c r="G25" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
@@ -1766,7 +1797,9 @@
       <c r="F27" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="24"/>
+      <c r="G27" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
@@ -1791,7 +1824,9 @@
       <c r="F28" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="24"/>
+      <c r="G28" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
@@ -1840,7 +1875,9 @@
       <c r="F30" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="24"/>
+      <c r="G30" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -1865,7 +1902,9 @@
       <c r="F31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="24"/>
+      <c r="G31" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
@@ -1932,7 +1971,7 @@
       <c r="F34" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="24"/>
+      <c r="G34" s="28"/>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
@@ -1957,7 +1996,9 @@
       <c r="F35" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="24"/>
+      <c r="G35" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
@@ -2006,7 +2047,9 @@
       <c r="F37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="24"/>
+      <c r="G37" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
@@ -2028,7 +2071,9 @@
       <c r="E38" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G38" s="24"/>
+      <c r="G38" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
@@ -2053,7 +2098,9 @@
       <c r="F39" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G39" s="24"/>
+      <c r="G39" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
@@ -2078,7 +2125,7 @@
       <c r="F40" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G40" s="24"/>
+      <c r="G40" s="28"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
@@ -2121,7 +2168,7 @@
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="24"/>
+      <c r="G42" s="28"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
@@ -2146,7 +2193,9 @@
       <c r="F43" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="24"/>
+      <c r="G43" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
@@ -2171,7 +2220,9 @@
       <c r="F44" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="24"/>
+      <c r="G44" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
@@ -2196,7 +2247,7 @@
       <c r="F45" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="24"/>
+      <c r="G45" s="28"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
@@ -2242,7 +2293,9 @@
       <c r="F47" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="24"/>
+      <c r="G47" s="28" t="s">
+        <v>161</v>
+      </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
@@ -2330,7 +2383,9 @@
       <c r="E51" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="23"/>
+      <c r="G51" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
@@ -2418,6 +2473,9 @@
       <c r="F55" s="14" t="s">
         <v>161</v>
       </c>
+      <c r="G55" s="27" t="s">
+        <v>161</v>
+      </c>
       <c r="H55" s="14"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
@@ -2439,6 +2497,9 @@
       <c r="E56" s="10" t="s">
         <v>106</v>
       </c>
+      <c r="G56" s="27" t="s">
+        <v>161</v>
+      </c>
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
@@ -2460,7 +2521,7 @@
       <c r="E57" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G57" s="23"/>
+      <c r="G57" s="26"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
@@ -2593,6 +2654,9 @@
       <c r="F63" s="14" t="s">
         <v>161</v>
       </c>
+      <c r="G63" s="27" t="s">
+        <v>161</v>
+      </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
@@ -2614,7 +2678,7 @@
       <c r="E64" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G64" s="23"/>
+      <c r="G64" s="26"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
@@ -2678,7 +2742,9 @@
       <c r="E67" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G67" s="23"/>
+      <c r="G67" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
@@ -2724,7 +2790,9 @@
       <c r="F69" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="23"/>
+      <c r="G69" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
@@ -2749,7 +2817,9 @@
       <c r="F70" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="23"/>
+      <c r="G70" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
@@ -2774,7 +2844,9 @@
       <c r="F71" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G71" s="23"/>
+      <c r="G71" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
@@ -2799,7 +2871,9 @@
       <c r="F72" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G72" s="23"/>
+      <c r="G72" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
@@ -2824,7 +2898,9 @@
       <c r="F73" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G73" s="23"/>
+      <c r="G73" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
@@ -2889,7 +2965,9 @@
       <c r="F76" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G76" s="23"/>
+      <c r="G76" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
@@ -2912,7 +2990,7 @@
         <v>106</v>
       </c>
       <c r="F77" s="19"/>
-      <c r="G77" s="23"/>
+      <c r="G77" s="26"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
@@ -2925,10 +3003,21 @@
       <c r="B78" s="21" t="s">
         <v>165</v>
       </c>
+      <c r="G78" s="27"/>
       <c r="L78" s="22"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F79" s="20"/>
+    <row r="79" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="23">
+        <v>78</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" s="27"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F80" s="20"/>
+      <c r="G80" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -599,7 +599,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -621,6 +621,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -851,14 +857,17 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1179,7 +1188,8 @@
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" customWidth="1"/>
     <col min="6" max="6" width="12.54296875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
@@ -1201,10 +1211,12 @@
       <c r="F1" s="24">
         <v>46042</v>
       </c>
-      <c r="G1" s="25">
+      <c r="G1" s="27">
         <v>46043</v>
       </c>
-      <c r="H1" s="14"/>
+      <c r="H1" s="25">
+        <v>46044</v>
+      </c>
       <c r="I1" s="14"/>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
@@ -1228,10 +1240,12 @@
       <c r="F2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="14"/>
+      <c r="G2" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
@@ -1252,7 +1266,9 @@
       <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
@@ -1273,7 +1289,7 @@
       <c r="E4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -1294,7 +1310,7 @@
       <c r="E5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="26"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -1315,7 +1331,9 @@
       <c r="E6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
@@ -1336,8 +1354,8 @@
       <c r="E7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="14"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="26"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
       <c r="K7" s="14"/>
@@ -1358,7 +1376,7 @@
       <c r="E8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="26"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -1379,7 +1397,9 @@
       <c r="E9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="14"/>
+      <c r="H9" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
@@ -1403,10 +1423,12 @@
       <c r="F10" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="14"/>
+      <c r="G10" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
@@ -1427,7 +1449,7 @@
       <c r="E11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="14"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
@@ -1448,7 +1470,7 @@
       <c r="E12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="26"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
@@ -1472,10 +1494,12 @@
       <c r="F13" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G13" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="14"/>
+      <c r="G13" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="14"/>
@@ -1496,10 +1520,12 @@
       <c r="E14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="14"/>
+      <c r="G14" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
@@ -1520,7 +1546,7 @@
       <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="26"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
@@ -1541,8 +1567,8 @@
       <c r="E16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="14"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="26"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
@@ -1563,8 +1589,8 @@
       <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="14"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="26"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="14"/>
@@ -1585,7 +1611,7 @@
       <c r="E18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="26"/>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
@@ -1606,7 +1632,9 @@
       <c r="E19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
@@ -1627,7 +1655,7 @@
       <c r="E20" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
@@ -1651,10 +1679,12 @@
       <c r="F21" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="14"/>
+      <c r="G21" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
@@ -1675,7 +1705,7 @@
       <c r="E22" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="26"/>
       <c r="I22" s="14">
         <v>1</v>
       </c>
@@ -1698,7 +1728,7 @@
       <c r="E23" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="26"/>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
       <c r="K23" s="14"/>
@@ -1722,10 +1752,12 @@
       <c r="F24" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="14"/>
+      <c r="G24" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
@@ -1749,10 +1781,12 @@
       <c r="F25" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="14"/>
+      <c r="G25" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
@@ -1773,7 +1807,7 @@
       <c r="E26" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="14"/>
+      <c r="H26" s="26"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
@@ -1797,10 +1831,12 @@
       <c r="F27" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="14"/>
+      <c r="G27" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="K27" s="14"/>
@@ -1824,10 +1860,10 @@
       <c r="F28" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H28" s="14"/>
+      <c r="G28" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H28" s="26"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="K28" s="14"/>
@@ -1851,7 +1887,7 @@
       <c r="F29" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="26"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
       <c r="K29" s="14"/>
@@ -1875,10 +1911,12 @@
       <c r="F30" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="14"/>
+      <c r="G30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
@@ -1902,10 +1940,12 @@
       <c r="F31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="14"/>
+      <c r="G31" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
       <c r="K31" s="14"/>
@@ -1926,7 +1966,7 @@
       <c r="E32" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H32" s="14"/>
+      <c r="H32" s="26"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
       <c r="K32" s="14"/>
@@ -1947,7 +1987,7 @@
       <c r="E33" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="14"/>
+      <c r="H33" s="26"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14"/>
@@ -1971,8 +2011,8 @@
       <c r="F34" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="28"/>
-      <c r="H34" s="14"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="26"/>
       <c r="I34" s="14"/>
       <c r="J34" s="14"/>
       <c r="K34" s="14"/>
@@ -1996,10 +2036,12 @@
       <c r="F35" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="14"/>
+      <c r="G35" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14"/>
       <c r="K35" s="14"/>
@@ -2023,7 +2065,7 @@
       <c r="F36" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H36" s="14"/>
+      <c r="H36" s="26"/>
       <c r="I36" s="14"/>
       <c r="J36" s="14"/>
       <c r="K36" s="14"/>
@@ -2047,10 +2089,10 @@
       <c r="F37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="14"/>
+      <c r="G37" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="26"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
@@ -2071,10 +2113,10 @@
       <c r="E38" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G38" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="14"/>
+      <c r="G38" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="26"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
       <c r="K38" s="14"/>
@@ -2098,10 +2140,12 @@
       <c r="F39" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G39" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="14"/>
+      <c r="G39" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
       <c r="K39" s="14"/>
@@ -2125,8 +2169,8 @@
       <c r="F40" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G40" s="28"/>
-      <c r="H40" s="14"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="26"/>
       <c r="I40" s="14"/>
       <c r="J40" s="14"/>
       <c r="K40" s="14"/>
@@ -2147,7 +2191,7 @@
       <c r="E41" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="14"/>
+      <c r="H41" s="26"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14"/>
       <c r="K41" s="14"/>
@@ -2168,8 +2212,10 @@
       <c r="E42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="28"/>
-      <c r="H42" s="14"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14"/>
       <c r="K42" s="14"/>
@@ -2193,10 +2239,12 @@
       <c r="F43" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="14"/>
+      <c r="G43" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
       <c r="K43" s="14"/>
@@ -2220,10 +2268,12 @@
       <c r="F44" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" s="14"/>
+      <c r="G44" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14"/>
       <c r="K44" s="14"/>
@@ -2247,8 +2297,10 @@
       <c r="F45" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="28"/>
-      <c r="H45" s="14"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14"/>
       <c r="K45" s="14"/>
@@ -2269,7 +2321,9 @@
       <c r="E46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="14"/>
+      <c r="H46" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14"/>
       <c r="K46" s="14"/>
@@ -2293,10 +2347,12 @@
       <c r="F47" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" s="14"/>
+      <c r="G47" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14"/>
       <c r="K47" s="14"/>
@@ -2317,7 +2373,9 @@
       <c r="E48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="14"/>
+      <c r="H48" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14"/>
       <c r="K48" s="14"/>
@@ -2341,7 +2399,7 @@
       <c r="F49" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H49" s="14"/>
+      <c r="H49" s="26"/>
       <c r="I49" s="14"/>
       <c r="J49" s="14"/>
       <c r="K49" s="14"/>
@@ -2362,7 +2420,7 @@
       <c r="E50" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H50" s="14"/>
+      <c r="H50" s="26"/>
       <c r="I50" s="14"/>
       <c r="J50" s="14"/>
       <c r="K50" s="14"/>
@@ -2383,10 +2441,10 @@
       <c r="E51" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H51" s="14"/>
+      <c r="G51" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="26"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14"/>
       <c r="K51" s="14"/>
@@ -2407,7 +2465,7 @@
       <c r="E52" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H52" s="14"/>
+      <c r="H52" s="26"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14"/>
       <c r="K52" s="14"/>
@@ -2428,7 +2486,7 @@
       <c r="E53" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H53" s="14"/>
+      <c r="H53" s="26"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14"/>
       <c r="K53" s="14"/>
@@ -2449,7 +2507,7 @@
       <c r="E54" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="14"/>
+      <c r="H54" s="26"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14"/>
       <c r="K54" s="14"/>
@@ -2473,10 +2531,10 @@
       <c r="F55" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G55" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="H55" s="14"/>
+      <c r="G55" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="26"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="K55" s="14"/>
@@ -2497,10 +2555,10 @@
       <c r="E56" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G56" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="H56" s="14"/>
+      <c r="G56" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H56" s="26"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
       <c r="K56" s="14"/>
@@ -2521,8 +2579,8 @@
       <c r="E57" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G57" s="26"/>
-      <c r="H57" s="14"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="26"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
       <c r="K57" s="14"/>
@@ -2543,7 +2601,7 @@
       <c r="E58" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H58" s="14"/>
+      <c r="H58" s="26"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
       <c r="K58" s="14"/>
@@ -2564,7 +2622,7 @@
       <c r="E59" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H59" s="14"/>
+      <c r="H59" s="26"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
       <c r="K59" s="14"/>
@@ -2588,7 +2646,7 @@
       <c r="F60" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H60" s="14"/>
+      <c r="H60" s="26"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
       <c r="K60" s="14"/>
@@ -2609,7 +2667,9 @@
       <c r="E61" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H61" s="14"/>
+      <c r="H61" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
       <c r="K61" s="14"/>
@@ -2630,7 +2690,7 @@
       <c r="E62" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H62" s="14"/>
+      <c r="H62" s="26"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
       <c r="K62" s="14"/>
@@ -2654,10 +2714,12 @@
       <c r="F63" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G63" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="H63" s="14"/>
+      <c r="G63" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
       <c r="K63" s="14"/>
@@ -2678,8 +2740,8 @@
       <c r="E64" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G64" s="26"/>
-      <c r="H64" s="14"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="26"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
       <c r="K64" s="14"/>
@@ -2700,7 +2762,7 @@
       <c r="E65" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H65" s="14"/>
+      <c r="H65" s="26"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
       <c r="K65" s="14"/>
@@ -2721,7 +2783,7 @@
       <c r="E66" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H66" s="14"/>
+      <c r="H66" s="26"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14"/>
       <c r="K66" s="14"/>
@@ -2742,10 +2804,10 @@
       <c r="E67" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G67" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H67" s="14"/>
+      <c r="G67" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="26"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14"/>
       <c r="K67" s="14"/>
@@ -2766,7 +2828,7 @@
       <c r="E68" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H68" s="14"/>
+      <c r="H68" s="26"/>
       <c r="I68" s="14"/>
       <c r="J68" s="14"/>
       <c r="K68" s="14"/>
@@ -2790,10 +2852,12 @@
       <c r="F69" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="14"/>
+      <c r="G69" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
       <c r="K69" s="14"/>
@@ -2817,10 +2881,12 @@
       <c r="F70" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="14"/>
+      <c r="G70" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
       <c r="K70" s="14"/>
@@ -2844,10 +2910,12 @@
       <c r="F71" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G71" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="14"/>
+      <c r="G71" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
       <c r="K71" s="14"/>
@@ -2871,10 +2939,12 @@
       <c r="F72" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G72" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H72" s="14"/>
+      <c r="G72" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
       <c r="K72" s="14"/>
@@ -2898,10 +2968,12 @@
       <c r="F73" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G73" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="14"/>
+      <c r="G73" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I73" s="14"/>
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
@@ -2922,7 +2994,7 @@
       <c r="E74" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="H74" s="14"/>
+      <c r="H74" s="26"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
@@ -2943,7 +3015,7 @@
       <c r="E75" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H75" s="14"/>
+      <c r="H75" s="26"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
       <c r="K75" s="14"/>
@@ -2965,10 +3037,12 @@
       <c r="F76" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G76" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="14"/>
+      <c r="G76" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
@@ -2990,8 +3064,10 @@
         <v>106</v>
       </c>
       <c r="F77" s="19"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="14"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="26" t="s">
+        <v>161</v>
+      </c>
       <c r="I77" s="14"/>
       <c r="J77" s="14"/>
       <c r="K77" s="14"/>
@@ -3003,21 +3079,23 @@
       <c r="B78" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="G78" s="27"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="26"/>
       <c r="L78" s="22"/>
     </row>
-    <row r="79" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" s="14" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="23">
         <v>78</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="G79" s="27"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F80" s="20"/>
-      <c r="G80" s="29"/>
+      <c r="G80" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -1266,9 +1266,7 @@
       <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>161</v>
-      </c>
+      <c r="H3" s="26"/>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="168">
   <si>
     <t>Sr. No</t>
   </si>
@@ -535,13 +535,16 @@
   </si>
   <si>
     <t>Sanket Kunde</t>
+  </si>
+  <si>
+    <t>AA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,6 +599,25 @@
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -792,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -804,9 +826,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -834,19 +853,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -868,6 +874,37 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1185,11 +1222,15 @@
   <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.08984375" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.81640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="4.26953125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="3.6328125" style="26" customWidth="1"/>
+    <col min="9" max="9" width="1.90625" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
@@ -1205,50 +1246,56 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24">
+      <c r="F1" s="18">
         <v>46042</v>
       </c>
-      <c r="G1" s="27">
+      <c r="G1" s="21">
         <v>46043</v>
       </c>
-      <c r="H1" s="25">
+      <c r="H1" s="19">
         <v>46044</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
+      <c r="I1" s="18">
+        <v>46045</v>
+      </c>
+      <c r="J1" s="18">
+        <v>46049</v>
+      </c>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="28">
         <v>7709797922</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="E2" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
@@ -1263,13 +1310,13 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
@@ -1284,13 +1331,13 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
+      <c r="E4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
@@ -1305,13 +1352,13 @@
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
+      <c r="E5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
@@ -1326,15 +1373,15 @@
       <c r="D6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
@@ -1349,14 +1396,14 @@
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+      <c r="E7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
@@ -1371,13 +1418,13 @@
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="26"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="E8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
@@ -1392,44 +1439,48 @@
       <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
+      <c r="E9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+    </row>
+    <row r="10" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="27">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="28">
         <v>9503424123</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="E10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" spans="1:11" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
@@ -1444,13 +1495,13 @@
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="E11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
@@ -1465,42 +1516,46 @@
       <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-    </row>
-    <row r="13" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
+      <c r="E12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="28">
         <v>9112924669</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
+      <c r="E13" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="30"/>
     </row>
     <row r="14" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
@@ -1515,18 +1570,20 @@
       <c r="D14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
+      <c r="E14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
@@ -1541,13 +1598,15 @@
       <c r="D15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
@@ -1562,14 +1621,14 @@
       <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+      <c r="E16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
@@ -1584,14 +1643,14 @@
       <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
+      <c r="E17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
     </row>
     <row r="18" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
@@ -1606,13 +1665,15 @@
       <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
@@ -1627,15 +1688,13 @@
       <c r="D19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
+      <c r="E19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
     </row>
     <row r="20" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
@@ -1650,42 +1709,42 @@
       <c r="D20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-    </row>
-    <row r="21" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
+      <c r="E20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="28">
         <v>7350486446</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+      <c r="E21" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
@@ -1700,15 +1759,15 @@
       <c r="D22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="26"/>
-      <c r="I22" s="14">
+      <c r="E22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="13">
         <v>1</v>
       </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
     </row>
     <row r="23" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
@@ -1723,71 +1782,75 @@
       <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-    </row>
-    <row r="24" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2">
+      <c r="E23" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="28">
         <v>9890737620</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-    </row>
-    <row r="25" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2">
+      <c r="E24" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+    </row>
+    <row r="25" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="28">
         <v>7499115466</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
+      <c r="E25" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
@@ -1802,69 +1865,75 @@
       <c r="D26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-    </row>
-    <row r="27" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" s="36" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>7249155158</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-    </row>
-    <row r="28" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2">
+      <c r="E27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+    </row>
+    <row r="28" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="27">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="28">
         <v>7387857040</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
+      <c r="E28" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H28" s="32"/>
+      <c r="I28" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J28" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K28" s="30"/>
     </row>
     <row r="29" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
@@ -1879,74 +1948,82 @@
       <c r="D29" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-    </row>
-    <row r="30" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="2">
+      <c r="E29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="27">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="28">
         <v>9503578446</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-    </row>
-    <row r="31" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="2">
+      <c r="E30" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K30" s="30"/>
+    </row>
+    <row r="31" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="27">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="28">
         <v>9226731346</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
+      <c r="E31" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
@@ -1961,13 +2038,13 @@
       <c r="D32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" s="26"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
+      <c r="E32" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" s="20"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
     </row>
     <row r="33" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
@@ -1982,13 +2059,13 @@
       <c r="D33" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" s="26"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
+      <c r="E33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="20"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
@@ -2003,46 +2080,50 @@
       <c r="D34" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="30"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-    </row>
-    <row r="35" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="2">
+      <c r="E34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="24"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="27">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="28">
         <v>7715045931</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
+      <c r="E35" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J35" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K35" s="30"/>
     </row>
     <row r="36" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
@@ -2057,43 +2138,49 @@
       <c r="D36" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H36" s="26"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-    </row>
-    <row r="37" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="2">
+      <c r="E36" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="20"/>
+      <c r="I36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="27">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="28">
         <v>8010613326</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
+      <c r="E37" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="32"/>
+      <c r="I37" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
@@ -2108,16 +2195,18 @@
       <c r="D38" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
+      <c r="E38" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="20"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K38" s="13"/>
     </row>
     <row r="39" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
@@ -2132,21 +2221,23 @@
       <c r="D39" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G39" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
+      <c r="E39" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
     </row>
     <row r="40" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
@@ -2161,17 +2252,19 @@
       <c r="D40" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
+      <c r="F40" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G40" s="24"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K40" s="13"/>
     </row>
     <row r="41" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
@@ -2186,13 +2279,13 @@
       <c r="D41" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="26"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
+      <c r="E41" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="20"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
     </row>
     <row r="42" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
@@ -2207,74 +2300,78 @@
       <c r="D42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="30"/>
-      <c r="H42" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-    </row>
-    <row r="43" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="2">
+      <c r="E42" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="24"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="27">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="28">
         <v>9064193565</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G43" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-    </row>
-    <row r="44" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="2">
+      <c r="E43" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="32"/>
+      <c r="I43" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K43" s="30"/>
+    </row>
+    <row r="44" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="27">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="28">
         <v>9021750609</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
+      <c r="E44" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J44" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K44" s="30"/>
     </row>
     <row r="45" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
@@ -2289,19 +2386,19 @@
       <c r="D45" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="30"/>
-      <c r="H45" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
+      <c r="E45" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="24"/>
+      <c r="H45" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
     </row>
     <row r="46" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
@@ -2316,15 +2413,13 @@
       <c r="D46" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
+      <c r="E46" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
@@ -2339,21 +2434,21 @@
       <c r="D47" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F47" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G47" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
+      <c r="F47" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K47" s="13"/>
     </row>
     <row r="48" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
@@ -2368,15 +2463,15 @@
       <c r="D48" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
+      <c r="E48" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
@@ -2391,16 +2486,16 @@
       <c r="D49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F49" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
+      <c r="F49" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="20"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
     </row>
     <row r="50" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
@@ -2415,13 +2510,13 @@
       <c r="D50" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
@@ -2436,16 +2531,16 @@
       <c r="D51" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
+      <c r="G51" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="20"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
     </row>
     <row r="52" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
@@ -2460,13 +2555,13 @@
       <c r="D52" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H52" s="26"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
@@ -2481,13 +2576,13 @@
       <c r="D53" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H53" s="26"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
     </row>
     <row r="54" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
@@ -2502,13 +2597,13 @@
       <c r="D54" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H54" s="26"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
@@ -2517,25 +2612,25 @@
       <c r="B55" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>8482971951</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G55" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="H55" s="26"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
+      <c r="F55" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="20"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
     </row>
     <row r="56" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
@@ -2550,16 +2645,16 @@
       <c r="D56" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G56" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="H56" s="26"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
+      <c r="G56" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H56" s="20"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
@@ -2574,14 +2669,14 @@
       <c r="D57" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G57" s="28"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
     </row>
     <row r="58" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
@@ -2596,13 +2691,15 @@
       <c r="D58" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H58" s="26"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
@@ -2617,13 +2714,13 @@
       <c r="D59" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H59" s="26"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
     </row>
     <row r="60" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
@@ -2632,22 +2729,22 @@
       <c r="B60" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="6">
         <v>8459123525</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H60" s="26"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
+      <c r="E60" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H60" s="20"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
     </row>
     <row r="61" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
@@ -2656,21 +2753,23 @@
       <c r="B61" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="6">
         <v>8010312022</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E61" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
+      <c r="E61" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
@@ -2679,19 +2778,19 @@
       <c r="B62" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="6">
         <v>7448160689</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H62" s="26"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
+      <c r="E62" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="20"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
     </row>
     <row r="63" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
@@ -2700,33 +2799,31 @@
       <c r="B63" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="6">
         <v>9922070611</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="H63" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
+      <c r="E63" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="20"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C64" s="3">
@@ -2735,14 +2832,16 @@
       <c r="D64" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G64" s="28"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
@@ -2757,13 +2856,13 @@
       <c r="D65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H65" s="26"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
@@ -2778,19 +2877,19 @@
       <c r="D66" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H66" s="26"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>139</v>
       </c>
       <c r="C67" s="3">
@@ -2799,16 +2898,18 @@
       <c r="D67" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G67" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H67" s="26"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
+      <c r="G67" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="20"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
@@ -2823,106 +2924,118 @@
       <c r="D68" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H68" s="26"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-    </row>
-    <row r="69" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="2">
+      <c r="H68" s="20"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+    </row>
+    <row r="69" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="27">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="28">
         <v>8451042496</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F69" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G69" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-    </row>
-    <row r="70" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="2">
+      <c r="F69" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G69" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J69" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K69" s="30"/>
+    </row>
+    <row r="70" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="27">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="28">
         <v>7666361933</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F70" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-    </row>
-    <row r="71" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="2">
+      <c r="F70" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I70" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J70" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K70" s="30"/>
+    </row>
+    <row r="71" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="27">
         <v>70</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="28">
         <v>7820816633</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F71" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G71" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
+      <c r="F71" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J71" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K71" s="30"/>
     </row>
     <row r="72" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>149</v>
       </c>
       <c r="C72" s="3">
@@ -2931,56 +3044,62 @@
       <c r="D72" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F72" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G72" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-    </row>
-    <row r="73" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="2">
+      <c r="F72" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G72" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+    </row>
+    <row r="73" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="27">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="28">
         <v>8767152381</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F73" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G73" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
+      <c r="F73" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I73" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J73" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K73" s="30"/>
     </row>
     <row r="74" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>153</v>
       </c>
       <c r="C74" s="3">
@@ -2989,19 +3108,19 @@
       <c r="D74" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H74" s="26"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
     </row>
     <row r="75" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>155</v>
       </c>
       <c r="C75" s="3">
@@ -3010,90 +3129,96 @@
       <c r="D75" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H75" s="26"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-    </row>
-    <row r="76" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="2">
+      <c r="H75" s="20"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+    </row>
+    <row r="76" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="27">
         <v>75</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="8" t="s">
+      <c r="C76" s="41"/>
+      <c r="D76" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="F76" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G76" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-    </row>
-    <row r="77" spans="1:12" ht="68" x14ac:dyDescent="0.35">
-      <c r="A77" s="15">
+      <c r="F76" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I76" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J76" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="K76" s="30"/>
+    </row>
+    <row r="77" spans="1:12" s="33" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+      <c r="A77" s="37">
         <v>76</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="17">
+      <c r="C77" s="38">
         <v>8237450604</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="F77" s="19"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-    </row>
-    <row r="78" spans="1:12" s="14" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="14">
+      <c r="F77" s="40"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+    </row>
+    <row r="78" spans="1:12" s="13" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="13">
         <v>77</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="G78" s="29"/>
-      <c r="H78" s="26"/>
-      <c r="L78" s="22"/>
-    </row>
-    <row r="79" spans="1:12" s="14" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="23">
+      <c r="G78" s="23"/>
+      <c r="H78" s="20"/>
+      <c r="L78" s="16"/>
+    </row>
+    <row r="79" spans="1:12" s="13" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="17">
         <v>78</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G79" s="29"/>
-      <c r="H79" s="26"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="20"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F80" s="20"/>
-      <c r="G80" s="31"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
   <si>
     <t>Sr. No</t>
   </si>
@@ -1226,11 +1226,12 @@
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
     <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.36328125" customWidth="1"/>
-    <col min="6" max="6" width="1.81640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="4.26953125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="3.6328125" style="26" customWidth="1"/>
-    <col min="9" max="9" width="1.90625" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="5.7265625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" style="26" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" customWidth="1"/>
+    <col min="10" max="10" width="4.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
@@ -1264,7 +1265,9 @@
       <c r="J1" s="18">
         <v>46049</v>
       </c>
-      <c r="K1" s="13"/>
+      <c r="K1" s="18">
+        <v>46051</v>
+      </c>
     </row>
     <row r="2" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="27">
@@ -1295,7 +1298,9 @@
       <c r="J2" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K2" s="30"/>
+      <c r="K2" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
@@ -1480,7 +1485,9 @@
       <c r="J10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K10" s="30"/>
+      <c r="K10" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
@@ -1555,7 +1562,9 @@
       <c r="J13" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="30"/>
+      <c r="K13" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
@@ -1583,7 +1592,9 @@
       <c r="J14" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="K14" s="13"/>
+      <c r="K14" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
@@ -1606,7 +1617,9 @@
       <c r="J15" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="K15" s="13"/>
+      <c r="K15" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
@@ -1744,7 +1757,9 @@
       </c>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="K21" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
@@ -1819,7 +1834,9 @@
         <v>161</v>
       </c>
       <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
+      <c r="K24" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="25" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="27">
@@ -1850,7 +1867,9 @@
         <v>161</v>
       </c>
       <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
+      <c r="K25" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
@@ -1933,7 +1952,9 @@
       <c r="J28" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K28" s="30"/>
+      <c r="K28" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
@@ -1990,7 +2011,9 @@
       <c r="J30" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K30" s="30"/>
+      <c r="K30" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="31" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="27">
@@ -2023,7 +2046,9 @@
       <c r="J31" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K31" s="30"/>
+      <c r="K31" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="32" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
@@ -2090,7 +2115,9 @@
       <c r="H34" s="20"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="K34" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="35" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="27">
@@ -2123,7 +2150,9 @@
       <c r="J35" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K35" s="30"/>
+      <c r="K35" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="36" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
@@ -2180,7 +2209,9 @@
       <c r="J37" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="30"/>
+      <c r="K37" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="38" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
@@ -2206,7 +2237,9 @@
       <c r="J38" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="K38" s="13"/>
+      <c r="K38" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="39" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
@@ -2264,7 +2297,9 @@
       <c r="J40" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="K40" s="13"/>
+      <c r="K40" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="41" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
@@ -2338,7 +2373,9 @@
       <c r="J43" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="K43" s="30"/>
+      <c r="K43" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="44" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="27">
@@ -2419,7 +2456,9 @@
       <c r="H46" s="20"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="K46" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="47" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
@@ -2448,7 +2487,9 @@
       <c r="J47" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="K47" s="13"/>
+      <c r="K47" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="48" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
@@ -2471,7 +2512,9 @@
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="K48" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
@@ -2495,7 +2538,9 @@
       <c r="H49" s="20"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="K49" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="50" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
@@ -2540,7 +2585,9 @@
       <c r="H51" s="20"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="K51" s="13" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="52" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$K$79</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -535,9 +538,6 @@
   </si>
   <si>
     <t>Sanket Kunde</t>
-  </si>
-  <si>
-    <t>AA</t>
   </si>
 </sst>
 </file>
@@ -814,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -905,6 +905,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1225,7 +1226,7 @@
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
     <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
     <col min="6" max="6" width="5.26953125" style="13" customWidth="1"/>
     <col min="7" max="7" width="5.7265625" style="23" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" style="26" customWidth="1"/>
@@ -1234,7 +1235,7 @@
     <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,24 +1251,12 @@
       <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18">
-        <v>46042</v>
-      </c>
-      <c r="G1" s="21">
-        <v>46043</v>
-      </c>
-      <c r="H1" s="19">
-        <v>46044</v>
-      </c>
-      <c r="I1" s="18">
-        <v>46045</v>
-      </c>
-      <c r="J1" s="18">
-        <v>46049</v>
-      </c>
-      <c r="K1" s="18">
-        <v>46051</v>
-      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="27">
@@ -1288,19 +1277,11 @@
       <c r="F2" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>161</v>
-      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="32"/>
       <c r="I2" s="30"/>
-      <c r="J2" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
@@ -1381,9 +1362,7 @@
       <c r="E6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="H6" s="20"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -1447,9 +1426,10 @@
       <c r="E9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="F9" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" s="20"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -1473,21 +1453,11 @@
       <c r="F10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K10" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" spans="1:11" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
@@ -1504,6 +1474,9 @@
       </c>
       <c r="E11" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="13"/>
@@ -1550,21 +1523,11 @@
       <c r="F13" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G13" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G13" s="31"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
     </row>
     <row r="14" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
@@ -1582,19 +1545,14 @@
       <c r="E14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="F14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="13"/>
-      <c r="J14" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
@@ -1614,12 +1572,8 @@
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="13"/>
-      <c r="J15" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
     </row>
     <row r="16" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
@@ -1683,9 +1637,7 @@
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J18" s="13"/>
       <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
@@ -1725,6 +1677,9 @@
       <c r="E20" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F20" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="H20" s="20"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
@@ -1749,17 +1704,11 @@
       <c r="F21" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>161</v>
-      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="32"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
-      <c r="K21" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
@@ -1778,9 +1727,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="20"/>
-      <c r="I22" s="13">
-        <v>1</v>
-      </c>
+      <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
     </row>
@@ -1824,19 +1771,11 @@
       <c r="F24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="K24" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="27">
@@ -1857,19 +1796,11 @@
       <c r="F25" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="30"/>
       <c r="J25" s="30"/>
-      <c r="K25" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
@@ -1908,18 +1839,10 @@
       <c r="E27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>161</v>
-      </c>
+      <c r="F27" s="34"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="34"/>
       <c r="J27" s="34"/>
       <c r="K27" s="34"/>
     </row>
@@ -1942,19 +1865,11 @@
       <c r="F28" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="31" t="s">
-        <v>161</v>
-      </c>
+      <c r="G28" s="31"/>
       <c r="H28" s="32"/>
-      <c r="I28" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J28" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K28" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
     </row>
     <row r="29" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
@@ -1971,9 +1886,6 @@
       </c>
       <c r="E29" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>161</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="13"/>
@@ -1999,21 +1911,11 @@
       <c r="F30" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I30" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J30" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K30" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G30" s="31"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
     </row>
     <row r="31" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="27">
@@ -2034,21 +1936,11 @@
       <c r="F31" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I31" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J31" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K31" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
@@ -2092,32 +1984,30 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
-    <row r="34" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="2">
+    <row r="34" spans="1:11" s="33" customFormat="1" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="27">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="28">
         <v>9580404186</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="24"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="E34" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
     </row>
     <row r="35" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="27">
@@ -2138,47 +2028,36 @@
       <c r="F35" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I35" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J35" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K35" s="30" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="2">
+      <c r="G35" s="31"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+    </row>
+    <row r="36" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="27">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="28">
         <v>8637738255</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+      <c r="E36" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="42"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
     </row>
     <row r="37" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="27">
@@ -2199,19 +2078,11 @@
       <c r="F37" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="31" t="s">
-        <v>161</v>
-      </c>
+      <c r="G37" s="31"/>
       <c r="H37" s="32"/>
-      <c r="I37" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J37" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K37" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
@@ -2229,48 +2100,37 @@
       <c r="E38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G38" s="24" t="s">
-        <v>161</v>
-      </c>
+      <c r="F38" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="24"/>
       <c r="H38" s="20"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K38" s="13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="2">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="27">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="28">
         <v>8180811404</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
+      <c r="E39" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="30"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
     </row>
     <row r="40" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
@@ -2294,12 +2154,8 @@
       <c r="G40" s="24"/>
       <c r="H40" s="20"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
     </row>
     <row r="41" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
@@ -2363,19 +2219,11 @@
       <c r="F43" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="31" t="s">
-        <v>161</v>
-      </c>
+      <c r="G43" s="31"/>
       <c r="H43" s="32"/>
-      <c r="I43" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J43" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="K43" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
     </row>
     <row r="44" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="27">
@@ -2396,18 +2244,10 @@
       <c r="F44" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I44" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J44" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G44" s="31"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
       <c r="K44" s="30"/>
     </row>
     <row r="45" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2430,9 +2270,7 @@
         <v>161</v>
       </c>
       <c r="G45" s="24"/>
-      <c r="H45" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="H45" s="20"/>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
       <c r="K45" s="13"/>
@@ -2456,9 +2294,7 @@
       <c r="H46" s="20"/>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
@@ -2479,17 +2315,11 @@
       <c r="F47" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="24" t="s">
-        <v>161</v>
-      </c>
+      <c r="G47" s="24"/>
       <c r="H47" s="20"/>
       <c r="I47" s="13"/>
-      <c r="J47" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
     </row>
     <row r="48" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
@@ -2507,14 +2337,10 @@
       <c r="E48" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="H48" s="20"/>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
-      <c r="K48" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
@@ -2532,15 +2358,10 @@
       <c r="E49" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F49" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="H49" s="20"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
-      <c r="K49" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="K49" s="13"/>
     </row>
     <row r="50" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
@@ -2579,15 +2400,11 @@
       <c r="E51" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="22" t="s">
-        <v>161</v>
-      </c>
+      <c r="G51" s="22"/>
       <c r="H51" s="20"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
-      <c r="K51" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="K51" s="13"/>
     </row>
     <row r="52" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
@@ -2626,6 +2443,9 @@
       <c r="E53" s="9" t="s">
         <v>106</v>
       </c>
+      <c r="F53" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="H53" s="20"/>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -2668,12 +2488,6 @@
       <c r="E55" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G55" s="23" t="s">
-        <v>161</v>
-      </c>
       <c r="H55" s="20"/>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -2694,9 +2508,6 @@
       </c>
       <c r="E56" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>161</v>
       </c>
       <c r="H56" s="20"/>
       <c r="I56" s="13"/>
@@ -2742,9 +2553,7 @@
         <v>106</v>
       </c>
       <c r="H58" s="20"/>
-      <c r="I58" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="I58" s="13"/>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
     </row>
@@ -2785,9 +2594,6 @@
       <c r="E60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="H60" s="20"/>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
@@ -2809,12 +2615,8 @@
       <c r="E61" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H61" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="H61" s="20"/>
+      <c r="I61" s="13"/>
       <c r="J61" s="13"/>
       <c r="K61" s="13"/>
     </row>
@@ -2855,12 +2657,6 @@
       <c r="E63" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F63" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>161</v>
-      </c>
       <c r="H63" s="20"/>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
@@ -2882,12 +2678,13 @@
       <c r="E64" s="9" t="s">
         <v>106</v>
       </c>
+      <c r="F64" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="G64" s="22"/>
       <c r="H64" s="20"/>
       <c r="I64" s="13"/>
-      <c r="J64" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J64" s="13"/>
       <c r="K64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
@@ -2948,14 +2745,10 @@
       <c r="E67" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G67" s="22" t="s">
-        <v>161</v>
-      </c>
+      <c r="G67" s="22"/>
       <c r="H67" s="20"/>
       <c r="I67" s="13"/>
-      <c r="J67" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="J67" s="13"/>
       <c r="K67" s="13"/>
     </row>
     <row r="68" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2998,18 +2791,10 @@
       <c r="F69" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I69" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J69" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G69" s="31"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
     <row r="70" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
@@ -3031,18 +2816,10 @@
       <c r="F70" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I70" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J70" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G70" s="31"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
     <row r="71" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
@@ -3064,18 +2841,10 @@
       <c r="F71" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G71" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I71" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J71" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G71" s="31"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
     <row r="72" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3094,18 +2863,9 @@
       <c r="E72" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F72" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G72" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H72" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>161</v>
-      </c>
+      <c r="G72" s="22"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="13"/>
       <c r="J72" s="13"/>
       <c r="K72" s="13"/>
     </row>
@@ -3128,18 +2888,10 @@
       <c r="F73" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G73" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I73" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J73" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="G73" s="31"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
     <row r="74" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
@@ -3179,6 +2931,9 @@
       <c r="E75" s="9" t="s">
         <v>106</v>
       </c>
+      <c r="F75" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="H75" s="20"/>
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
@@ -3201,18 +2956,10 @@
       <c r="F76" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G76" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I76" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="J76" s="30" t="s">
-        <v>167</v>
-      </c>
+      <c r="G76" s="31"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
     <row r="77" spans="1:12" s="33" customFormat="1" ht="68" x14ac:dyDescent="0.35">
@@ -3231,14 +2978,12 @@
       <c r="E77" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="F77" s="40"/>
+      <c r="F77" s="40" t="s">
+        <v>161</v>
+      </c>
       <c r="G77" s="31"/>
-      <c r="H77" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="I77" s="30" t="s">
-        <v>161</v>
-      </c>
+      <c r="H77" s="32"/>
+      <c r="I77" s="30"/>
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
@@ -3259,6 +3004,9 @@
       </c>
       <c r="B79" s="15" t="s">
         <v>166</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="G79" s="23"/>
       <c r="H79" s="20"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -1277,7 +1277,9 @@
       <c r="F2" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="31"/>
+      <c r="G2" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H2" s="32"/>
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
@@ -1340,6 +1342,9 @@
       </c>
       <c r="E5" s="9" t="s">
         <v>7</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>161</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="13"/>
@@ -1453,7 +1458,9 @@
       <c r="F10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="31"/>
+      <c r="G10" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H10" s="32"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
@@ -1523,7 +1530,9 @@
       <c r="F13" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H13" s="32"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
@@ -1548,7 +1557,9 @@
       <c r="F14" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="22"/>
+      <c r="G14" s="22" t="s">
+        <v>161</v>
+      </c>
       <c r="H14" s="20"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
@@ -1677,9 +1688,6 @@
       <c r="E20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="H20" s="20"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
@@ -1704,7 +1712,9 @@
       <c r="F21" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H21" s="32"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
@@ -1771,7 +1781,9 @@
       <c r="F24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H24" s="32"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
@@ -1796,7 +1808,9 @@
       <c r="F25" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G25" s="31"/>
+      <c r="G25" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H25" s="32"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
@@ -1911,7 +1925,9 @@
       <c r="F30" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="31"/>
+      <c r="G30" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H30" s="32"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
@@ -1936,7 +1952,9 @@
       <c r="F31" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="31"/>
+      <c r="G31" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H31" s="32"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
@@ -2003,7 +2021,9 @@
       <c r="F34" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="31"/>
+      <c r="G34" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H34" s="32"/>
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
@@ -2028,7 +2048,9 @@
       <c r="F35" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="31"/>
+      <c r="G35" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H35" s="32"/>
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
@@ -2053,7 +2075,9 @@
       <c r="F36" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G36" s="42"/>
+      <c r="G36" s="42" t="s">
+        <v>161</v>
+      </c>
       <c r="H36" s="32"/>
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
@@ -2078,59 +2102,63 @@
       <c r="F37" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="31"/>
+      <c r="G37" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H37" s="32"/>
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
       <c r="K37" s="30"/>
     </row>
-    <row r="38" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="2">
+    <row r="38" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="27">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="28">
         <v>8180987781</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G38" s="24"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-    </row>
-    <row r="39" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="27">
+      <c r="E38" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="32"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+    </row>
+    <row r="39" spans="1:11" s="36" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="3">
         <v>8180811404</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="30"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
+      <c r="E39" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="34"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
     </row>
     <row r="40" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
@@ -2194,7 +2222,9 @@
       <c r="E42" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="24"/>
+      <c r="G42" s="24" t="s">
+        <v>161</v>
+      </c>
       <c r="H42" s="20"/>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -2219,7 +2249,9 @@
       <c r="F43" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="31"/>
+      <c r="G43" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H43" s="32"/>
       <c r="I43" s="30"/>
       <c r="J43" s="30"/>
@@ -2244,7 +2276,9 @@
       <c r="F44" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="31"/>
+      <c r="G44" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H44" s="32"/>
       <c r="I44" s="30"/>
       <c r="J44" s="30"/>
@@ -2269,7 +2303,9 @@
       <c r="F45" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="24"/>
+      <c r="G45" s="24" t="s">
+        <v>161</v>
+      </c>
       <c r="H45" s="20"/>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
@@ -2315,7 +2351,9 @@
       <c r="F47" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="24"/>
+      <c r="G47" s="24" t="s">
+        <v>161</v>
+      </c>
       <c r="H47" s="20"/>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
@@ -2358,6 +2396,9 @@
       <c r="E49" s="9" t="s">
         <v>103</v>
       </c>
+      <c r="G49" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="H49" s="20"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -2400,7 +2441,9 @@
       <c r="E51" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="22"/>
+      <c r="G51" s="22" t="s">
+        <v>161</v>
+      </c>
       <c r="H51" s="20"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
@@ -2487,6 +2530,9 @@
       </c>
       <c r="E55" s="9" t="s">
         <v>106</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>161</v>
       </c>
       <c r="H55" s="20"/>
       <c r="I55" s="13"/>
@@ -2657,6 +2703,9 @@
       <c r="E63" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="G63" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="H63" s="20"/>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
@@ -2681,7 +2730,9 @@
       <c r="F64" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G64" s="22"/>
+      <c r="G64" s="22" t="s">
+        <v>161</v>
+      </c>
       <c r="H64" s="20"/>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
@@ -2767,6 +2818,9 @@
       <c r="E68" s="9" t="s">
         <v>106</v>
       </c>
+      <c r="G68" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="H68" s="20"/>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
@@ -2791,7 +2845,9 @@
       <c r="F69" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G69" s="31"/>
+      <c r="G69" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H69" s="32"/>
       <c r="I69" s="30"/>
       <c r="J69" s="30"/>
@@ -2816,7 +2872,9 @@
       <c r="F70" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="31"/>
+      <c r="G70" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H70" s="32"/>
       <c r="I70" s="30"/>
       <c r="J70" s="30"/>
@@ -2841,7 +2899,9 @@
       <c r="F71" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G71" s="31"/>
+      <c r="G71" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H71" s="32"/>
       <c r="I71" s="30"/>
       <c r="J71" s="30"/>
@@ -2888,7 +2948,9 @@
       <c r="F73" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G73" s="31"/>
+      <c r="G73" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H73" s="32"/>
       <c r="I73" s="30"/>
       <c r="J73" s="30"/>
@@ -2910,6 +2972,9 @@
       <c r="E74" s="9" t="s">
         <v>162</v>
       </c>
+      <c r="G74" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="H74" s="20"/>
       <c r="I74" s="13"/>
       <c r="J74" s="13"/>
@@ -2934,6 +2999,9 @@
       <c r="F75" s="13" t="s">
         <v>161</v>
       </c>
+      <c r="G75" s="23" t="s">
+        <v>161</v>
+      </c>
       <c r="H75" s="20"/>
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
@@ -2956,7 +3024,9 @@
       <c r="F76" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="G76" s="31"/>
+      <c r="G76" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H76" s="32"/>
       <c r="I76" s="30"/>
       <c r="J76" s="30"/>
@@ -2981,7 +3051,9 @@
       <c r="F77" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="G77" s="31"/>
+      <c r="G77" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="H77" s="32"/>
       <c r="I77" s="30"/>
       <c r="J77" s="30"/>

--- a/Attendance.xlsx
+++ b/Attendance.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="167">
   <si>
     <t>Sr. No</t>
   </si>
@@ -574,13 +574,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF3C4043"/>
-      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
@@ -620,8 +613,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,12 +637,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -831,10 +825,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -849,12 +840,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -863,49 +854,49 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1223,13 +1214,13 @@
   <dimension ref="A1:L80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" style="23" customWidth="1"/>
-    <col min="8" max="8" width="7.7265625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="5.7265625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" style="38" customWidth="1"/>
     <col min="9" max="9" width="5.81640625" customWidth="1"/>
     <col min="10" max="10" width="4.54296875" customWidth="1"/>
     <col min="11" max="11" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -1248,42 +1239,46 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-    </row>
-    <row r="2" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="27">
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+    </row>
+    <row r="2" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="24">
         <v>7709797922</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
+      <c r="E2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
@@ -1298,13 +1293,13 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="20"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
@@ -1319,13 +1314,13 @@
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="20"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
@@ -1340,16 +1335,16 @@
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="23" t="s">
+      <c r="E5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>161</v>
       </c>
       <c r="H5" s="20"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
@@ -1364,13 +1359,13 @@
       <c r="D6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="20"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
@@ -1385,14 +1380,14 @@
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="22"/>
+      <c r="E7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="20"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
@@ -1407,64 +1402,75 @@
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
+      <c r="E8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="23">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="24">
         <v>7821828784</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-    </row>
-    <row r="10" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="27">
+      <c r="E9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="23">
         <v>9</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="24">
         <v>9503424123</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
+      <c r="E10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" spans="1:11" ht="28" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
@@ -1479,16 +1485,13 @@
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>161</v>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="H11" s="20"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
@@ -1503,67 +1506,77 @@
       <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27">
+      <c r="E12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="23">
         <v>12</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="24">
         <v>9112924669</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-    </row>
-    <row r="14" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
+      <c r="E13" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+    </row>
+    <row r="14" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="23">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="24">
         <v>9322952417</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="E14" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
     </row>
     <row r="15" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
@@ -1578,13 +1591,13 @@
       <c r="D15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="20"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
@@ -1599,14 +1612,18 @@
       <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="E16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
     </row>
     <row r="17" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
@@ -1621,14 +1638,16 @@
       <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="22"/>
+      <c r="E17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="19"/>
       <c r="H17" s="20"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="I17" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
@@ -1643,13 +1662,13 @@
       <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="20"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
@@ -1664,13 +1683,17 @@
       <c r="D19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="E19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
@@ -1685,40 +1708,44 @@
       <c r="D20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H20" s="20"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27">
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23">
         <v>20</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="24">
         <v>7350486446</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="E21" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
     </row>
     <row r="22" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
@@ -1733,13 +1760,13 @@
       <c r="D22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H22" s="20"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
@@ -1754,67 +1781,75 @@
       <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H23" s="20"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-    </row>
-    <row r="24" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27">
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23">
         <v>23</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="24">
         <v>9890737620</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="32"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-    </row>
-    <row r="25" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27">
+      <c r="E24" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="23">
         <v>24</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="24">
         <v>7499115466</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="32"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
+      <c r="E25" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
     </row>
     <row r="26" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
@@ -1829,15 +1864,15 @@
       <c r="D26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H26" s="20"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="27" spans="1:11" s="36" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:11" s="30" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1850,40 +1885,44 @@
       <c r="D27" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-    </row>
-    <row r="28" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27">
+      <c r="E27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="23">
         <v>27</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="24">
         <v>7387857040</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
+      <c r="E28" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="27"/>
+      <c r="H28" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
     </row>
     <row r="29" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
@@ -1898,67 +1937,75 @@
       <c r="D29" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H29" s="20"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-    </row>
-    <row r="30" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="27">
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="23">
         <v>29</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="24">
         <v>9503578446</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-    </row>
-    <row r="31" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="27">
+      <c r="E30" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="23">
         <v>30</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="24">
         <v>9226731346</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
+      <c r="E31" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
     </row>
     <row r="32" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
@@ -1973,13 +2020,13 @@
       <c r="D32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H32" s="20"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
@@ -1994,150 +2041,168 @@
       <c r="D33" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H33" s="20"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-    </row>
-    <row r="34" spans="1:11" s="33" customFormat="1" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="27">
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" s="28" customFormat="1" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="23">
         <v>33</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="24">
         <v>9580404186</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-    </row>
-    <row r="35" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="27">
+      <c r="E34" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+    </row>
+    <row r="35" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="23">
         <v>34</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="24">
         <v>7715045931</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-    </row>
-    <row r="36" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="27">
+      <c r="E35" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+    </row>
+    <row r="36" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="23">
         <v>35</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="24">
         <v>8637738255</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-    </row>
-    <row r="37" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="27">
+      <c r="E36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+    </row>
+    <row r="37" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="23">
         <v>36</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="24">
         <v>8010613326</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E37" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-    </row>
-    <row r="38" spans="1:11" s="33" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="27">
+      <c r="E37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="23">
         <v>37</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="24">
         <v>8180987781</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38" s="32"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-    </row>
-    <row r="39" spans="1:11" s="36" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E38" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" s="30" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2150,15 +2215,15 @@
       <c r="D39" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="34"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
+      <c r="E39" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
     </row>
     <row r="40" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
@@ -2173,17 +2238,17 @@
       <c r="D40" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G40" s="24"/>
+      <c r="F40" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G40" s="21"/>
       <c r="H40" s="20"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
     </row>
     <row r="41" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
@@ -2198,13 +2263,13 @@
       <c r="D41" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H41" s="20"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
     </row>
     <row r="42" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
@@ -2219,70 +2284,78 @@
       <c r="D42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="24" t="s">
+      <c r="E42" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="21" t="s">
         <v>161</v>
       </c>
       <c r="H42" s="20"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="27">
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="23">
         <v>42</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="24">
         <v>9064193565</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-    </row>
-    <row r="44" spans="1:11" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="27">
+      <c r="E43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+    </row>
+    <row r="44" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="23">
         <v>43</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="24">
         <v>9021750609</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H44" s="32"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
+      <c r="E44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
     </row>
     <row r="45" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
@@ -2297,19 +2370,19 @@
       <c r="D45" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="24" t="s">
+      <c r="E45" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="21" t="s">
         <v>161</v>
       </c>
       <c r="H45" s="20"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
     </row>
     <row r="46" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
@@ -2324,40 +2397,44 @@
       <c r="D46" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H46" s="20"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-    </row>
-    <row r="47" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="2">
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="23">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="24">
         <v>8624085161</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="F47" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="F47" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
     </row>
     <row r="48" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
@@ -2372,13 +2449,13 @@
       <c r="D48" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="10" t="s">
         <v>7</v>
       </c>
       <c r="H48" s="20"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
     </row>
     <row r="49" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
@@ -2393,16 +2470,16 @@
       <c r="D49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="20" t="s">
         <v>161</v>
       </c>
       <c r="H49" s="20"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
     </row>
     <row r="50" spans="1:11" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
@@ -2417,37 +2494,42 @@
       <c r="D50" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="8" t="s">
         <v>164</v>
       </c>
       <c r="H50" s="20"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-    </row>
-    <row r="51" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="2">
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="23">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="24">
         <v>9067134679</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="G51" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
     </row>
     <row r="52" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
@@ -2462,13 +2544,13 @@
       <c r="D52" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H52" s="20"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
     </row>
     <row r="53" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
@@ -2483,16 +2565,16 @@
       <c r="D53" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="12" t="s">
         <v>161</v>
       </c>
       <c r="H53" s="20"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
     </row>
     <row r="54" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
@@ -2507,37 +2589,42 @@
       <c r="D54" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H54" s="20"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="2">
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="23">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="39">
         <v>8482971951</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="G55" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H55" s="20"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
     </row>
     <row r="56" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
@@ -2552,13 +2639,13 @@
       <c r="D56" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H56" s="20"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
     </row>
     <row r="57" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
@@ -2573,14 +2660,14 @@
       <c r="D57" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G57" s="22"/>
+      <c r="G57" s="19"/>
       <c r="H57" s="20"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
     </row>
     <row r="58" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
@@ -2595,13 +2682,13 @@
       <c r="D58" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H58" s="20"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
     </row>
     <row r="59" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
@@ -2616,13 +2703,13 @@
       <c r="D59" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H59" s="20"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
     </row>
     <row r="60" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
@@ -2631,19 +2718,21 @@
       <c r="B60" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>8459123525</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E60" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H60" s="20"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="E60" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
     </row>
     <row r="61" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
@@ -2652,19 +2741,21 @@
       <c r="B61" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>8010312022</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E61" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" s="20"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="E61" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
     </row>
     <row r="62" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
@@ -2673,70 +2764,77 @@
       <c r="B62" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>7448160689</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
         <v>7</v>
       </c>
       <c r="H62" s="20"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-    </row>
-    <row r="63" spans="1:11" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="2">
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" spans="1:11" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="23">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="24">
         <v>9922070611</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="E63" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H63" s="20"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
-    </row>
-    <row r="64" spans="1:11" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="2">
+      <c r="E63" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="26"/>
+      <c r="G63" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+    </row>
+    <row r="64" spans="1:11" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="23">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="24">
         <v>8788856918</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="E64" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F64" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G64" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H64" s="20"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
+      <c r="F64" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G64" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I64" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
     </row>
     <row r="65" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
@@ -2751,13 +2849,13 @@
       <c r="D65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H65" s="20"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="13"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
     </row>
     <row r="66" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
@@ -2772,19 +2870,19 @@
       <c r="D66" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="8" t="s">
         <v>106</v>
       </c>
       <c r="H66" s="20"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
     </row>
     <row r="67" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>139</v>
       </c>
       <c r="C67" s="3">
@@ -2793,14 +2891,14 @@
       <c r="D67" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G67" s="22"/>
+      <c r="G67" s="19"/>
       <c r="H67" s="20"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
     </row>
     <row r="68" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
@@ -2815,152 +2913,173 @@
       <c r="D68" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E68" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="20" t="s">
         <v>161</v>
       </c>
       <c r="H68" s="20"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-    </row>
-    <row r="69" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="27">
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="69" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="23">
         <v>68</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="24">
         <v>8451042496</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D69" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F69" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H69" s="32"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="30"/>
-      <c r="K69" s="30"/>
-    </row>
-    <row r="70" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="27">
+      <c r="F69" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G69" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+    </row>
+    <row r="70" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="23">
         <v>69</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="24">
         <v>7666361933</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F70" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="32"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-    </row>
-    <row r="71" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="27">
+      <c r="F70" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I70" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+    </row>
+    <row r="71" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="23">
         <v>70</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="24">
         <v>7820816633</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F71" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G71" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="32"/>
-      <c r="I71" s="30"/>
-      <c r="J71" s="30"/>
-      <c r="K71" s="30"/>
-    </row>
-    <row r="72" spans="1:12" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="2">
+      <c r="F71" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G71" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+    </row>
+    <row r="72" spans="1:12" s="28" customFormat="1" ht="68.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="23">
         <v>71</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="24">
         <v>7410760581</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E72" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="G72" s="22"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-    </row>
-    <row r="73" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="27">
+      <c r="F72" s="26"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+    </row>
+    <row r="73" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="23">
         <v>72</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="24">
         <v>8767152381</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D73" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F73" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="32"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="30"/>
-      <c r="K73" s="30"/>
+      <c r="F73" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I73" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
     </row>
     <row r="74" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C74" s="3">
@@ -2969,123 +3088,130 @@
       <c r="D74" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G74" s="23" t="s">
-        <v>161</v>
-      </c>
       <c r="H74" s="20"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-    </row>
-    <row r="75" spans="1:12" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="2">
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="23">
         <v>74</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="24">
         <v>9404215493</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="F75" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H75" s="20"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
-    </row>
-    <row r="76" spans="1:12" s="33" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="27">
+      <c r="F75" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G75" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H75" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+    </row>
+    <row r="76" spans="1:12" s="28" customFormat="1" ht="55" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="23">
         <v>75</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="41"/>
-      <c r="D76" s="28" t="s">
+      <c r="C76" s="35"/>
+      <c r="D76" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F76" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="32"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="30"/>
-      <c r="K76" s="30"/>
-    </row>
-    <row r="77" spans="1:12" s="33" customFormat="1" ht="68" x14ac:dyDescent="0.35">
-      <c r="A77" s="37">
+      <c r="F76" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G76" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I76" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+    </row>
+    <row r="77" spans="1:12" s="28" customFormat="1" ht="68" x14ac:dyDescent="0.35">
+      <c r="A77" s="31">
         <v>76</v>
       </c>
-      <c r="B77" s="38" t="s">
+      <c r="B77" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="38">
+      <c r="C77" s="32">
         <v>8237450604</v>
       </c>
-      <c r="D77" s="38" t="s">
+      <c r="D77" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="E77" s="39" t="s">
+      <c r="E77" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="F77" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G77" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H77" s="32"/>
-      <c r="I77" s="30"/>
-      <c r="J77" s="30"/>
-      <c r="K77" s="30"/>
-    </row>
-    <row r="78" spans="1:12" s="13" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="13">
+      <c r="F77" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="G77" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H77" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+    </row>
+    <row r="78" spans="1:12" s="12" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="12">
         <v>77</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G78" s="23"/>
+      <c r="G78" s="20"/>
       <c r="H78" s="20"/>
-      <c r="L78" s="16"/>
-    </row>
-    <row r="79" spans="1:12" s="13" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="17">
+      <c r="L78" s="15"/>
+    </row>
+    <row r="79" spans="1:12" s="12" customFormat="1" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="16">
         <v>78</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="F79" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G79" s="23"/>
+      <c r="F79" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G79" s="20"/>
       <c r="H79" s="20"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="F80" s="14"/>
-      <c r="G80" s="25"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
